--- a/business_forms/037_process_optimization_accelerator_application_form--business_forms.xlsx
+++ b/business_forms/037_process_optimization_accelerator_application_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'improve_process',_'label':_'improve_process'}</t>
+          <t>improve_process</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Improve Process', 'label': 'Improve Process'}</t>
+          <t>Improve Process</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'reduce_process',_'label':_'reduce_process'}</t>
+          <t>reduce_process</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Reduce Process', 'label': 'Reduce Process'}</t>
+          <t>Reduce Process</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'eliminate_process',_'label':_'eliminate_process'}</t>
+          <t>eliminate_process</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Eliminate Process', 'label': 'Eliminate Process'}</t>
+          <t>Eliminate Process</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'analyze',_'label':_'analyze'}</t>
+          <t>analyze</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Analyze', 'label': 'Analyze'}</t>
+          <t>Analyze</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'implement',_'label':_'implement'}</t>
+          <t>implement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Implement', 'label': 'Implement'}</t>
+          <t>Implement</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'test',_'label':_'test'}</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Test', 'label': 'Test'}</t>
+          <t>Test</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_0,_'label':_'est/edt'}</t>
+          <t>est/edt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 0, 'label': 'EST/EDT'}</t>
+          <t>EST/EDT</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'cdt'}</t>
+          <t>cdt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'CDT'}</t>
+          <t>CDT</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'mst/mdt'}</t>
+          <t>mst/mdt</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'MST/MDT'}</t>
+          <t>MST/MDT</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'pst/pdt'}</t>
+          <t>pst/pdt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'PST/PDT'}</t>
+          <t>PST/PDT</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'company',_'label':_'company'}</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Company', 'label': 'Company'}</t>
+          <t>Company</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'organization',_'label':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Organization', 'label': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'team',_'label':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Team', 'label': 'Team'}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'1-10',_'label':_'1-10'}</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': '1-10', 'label': '1-10'}</t>
+          <t>1-10</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'11-50',_'label':_'11-50'}</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': '11-50', 'label': '11-50'}</t>
+          <t>11-50</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'51-100',_'label':_'51-100'}</t>
+          <t>51-100</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': '51-100', 'label': '51-100'}</t>
+          <t>51-100</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'101-200',_'label':_'101-200'}</t>
+          <t>101-200</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': '101-200', 'label': '101-200'}</t>
+          <t>101-200</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'201-500',_'label':_'201-500'}</t>
+          <t>201-500</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': '201-500', 'label': '201-500'}</t>
+          <t>201-500</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'501-1000',_'label':_'501-1000'}</t>
+          <t>501-1000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': '501-1000', 'label': '501-1000'}</t>
+          <t>501-1000</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'1000+',_'label':_'1000+'}</t>
+          <t>1000+</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': '1000+', 'label': '1000+'}</t>
+          <t>1000+</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'physical',_'label':_'physical'}</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Physical', 'label': 'Physical'}</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'hybrid',_'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Hybrid', 'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'chat',_'label':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Chat', 'label': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'option1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Option1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'option2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Option2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'option3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Option3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'option4',_'label':_'option_4'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Option4', 'label': 'Option 4'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'option5',_'label':_'option_5'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Option5', 'label': 'Option 5'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
